--- a/code/data/numbers/w0wacdm-free.xlsx
+++ b/code/data/numbers/w0wacdm-free.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/852b2bada49559ee/code_final/data/numbers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\28943\OneDrive\NeutrinoForecast_J-PAS_PFS\code\data\numbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_085D37EF124C0C0F6235547658B6E63C80719F90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A53C86-09AD-4109-8A81-B52C5F3403BF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A004F-2B43-4A84-997B-CB3F7ED556BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="18720" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="437" windowWidth="18720" windowHeight="11434" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -156,14 +161,14 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -474,10 +479,9 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.765625" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="5"/>
-    <col min="4" max="4" width="9.23046875" style="6"/>
-    <col min="5" max="6" width="9.23046875" style="5"/>
+    <col min="2" max="3" width="9.23046875" style="3"/>
+    <col min="4" max="4" width="9.23046875" style="5"/>
+    <col min="5" max="6" width="9.23046875" style="3"/>
     <col min="7" max="9" width="9.23046875" style="7"/>
     <col min="10" max="10" width="9.23046875" style="9"/>
   </cols>
@@ -489,7 +493,7 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -498,13 +502,13 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="8" t="s">
@@ -515,320 +519,320 @@
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5">
-        <v>7.5713011224779553E-2</v>
-      </c>
-      <c r="C2" s="5">
-        <v>7.2139091706885441E-2</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1.109958880816735E-2</v>
-      </c>
-      <c r="E2" s="5">
-        <v>6.6609986821947201E-2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>3.453454672387979E-3</v>
+      <c r="B2" s="3">
+        <v>8.283363875202486E-2</v>
+      </c>
+      <c r="C2" s="3">
+        <v>7.8699194955131155E-2</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.214001055684908E-2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7.2504015396364738E-2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.4556163548150141E-3</v>
       </c>
       <c r="G2" s="7">
-        <v>0.149719170102489</v>
+        <v>0.14986293729878239</v>
       </c>
       <c r="H2" s="7">
-        <v>5.2866981731732113E-2</v>
+        <v>5.3176638057436977E-2</v>
       </c>
       <c r="I2" s="7">
-        <v>0.53043423130682665</v>
+        <v>0.54658321385805231</v>
       </c>
       <c r="J2" s="9">
-        <v>1.5256409451310839</v>
+        <v>1.5222427955669049</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5">
-        <v>2.5590710293897902E-2</v>
-      </c>
-      <c r="C3" s="5">
-        <v>3.5558174751681181E-2</v>
-      </c>
-      <c r="D3" s="6">
-        <v>8.8384097839813124E-3</v>
-      </c>
-      <c r="E3" s="5">
-        <v>4.1078673423945077E-2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>4.3005393886991157E-2</v>
+      <c r="B3" s="3">
+        <v>2.55907102938976E-2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.5558174751681278E-2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>8.8384097839812898E-3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.1078673423944993E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4.3005393886991088E-2</v>
       </c>
       <c r="G3" s="7">
-        <v>0.45288067482870609</v>
+        <v>0.45288067482869748</v>
       </c>
       <c r="H3" s="7">
-        <v>0.79676270985011877</v>
+        <v>0.79676270985016417</v>
       </c>
       <c r="I3" s="7">
-        <v>0.15942091445831399</v>
+        <v>0.15942091445831491</v>
       </c>
       <c r="J3" s="9">
-        <v>0.83791179220378975</v>
+        <v>0.83791179220378875</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5">
-        <v>3.9352030121759647E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>5.2647073608221531E-2</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1.2963619543753659E-2</v>
-      </c>
-      <c r="E4" s="5">
-        <v>5.3527685856307412E-2</v>
-      </c>
-      <c r="F4" s="5">
-        <v>7.285533126880217E-2</v>
+      <c r="B4" s="3">
+        <v>3.935203012175837E-2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5.2647073608221587E-2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1.29636195437536E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5.3527685856308002E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>7.2855331268801934E-2</v>
       </c>
       <c r="G4" s="7">
-        <v>0.60305272682356925</v>
+        <v>0.60305272682359778</v>
       </c>
       <c r="H4" s="7">
-        <v>1.1916402608349721</v>
+        <v>1.191640260835036</v>
       </c>
       <c r="I4" s="7">
-        <v>0.2349471382714636</v>
+        <v>0.23494713827147171</v>
       </c>
       <c r="J4" s="9">
-        <v>1.155277805396695</v>
+        <v>1.1552778053967001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5">
-        <v>5.0988647766487552E-2</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.13604637969964109</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2.8274265082802681E-2</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.14126378950083329</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.12475250927404261</v>
+      <c r="B5" s="3">
+        <v>5.0988647766491382E-2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1360463796996475</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2.8274265082803372E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.14126378950084981</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.12475250927405079</v>
       </c>
       <c r="G5" s="7">
-        <v>0.75212675820045549</v>
+        <v>0.75212675820052299</v>
       </c>
       <c r="H5" s="7">
-        <v>2.412089541545996</v>
+        <v>2.4120895415459929</v>
       </c>
       <c r="I5" s="7">
-        <v>1.1429027877074021</v>
+        <v>1.1429027877074229</v>
       </c>
       <c r="J5" s="9">
-        <v>3.3842776661074581</v>
+        <v>3.3842776661076002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
-        <v>4.6681961325305978E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <v>5.2052598705868501E-2</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1.1234446372484431E-2</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.10781307764357639</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.11033943650286709</v>
+      <c r="B6" s="3">
+        <v>4.6681961325301238E-2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.2052598705862367E-2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1.123444637248411E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.1078130776435655</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.11033943650285701</v>
       </c>
       <c r="G6" s="7">
-        <v>0.81828640020379062</v>
+        <v>0.81828640020375276</v>
       </c>
       <c r="H6" s="7">
-        <v>2.542315733457277</v>
+        <v>2.5423157334570008</v>
       </c>
       <c r="I6" s="7">
-        <v>0.37219427509564912</v>
+        <v>0.37219427509564018</v>
       </c>
       <c r="J6" s="9">
-        <v>1.3424961445519881</v>
+        <v>1.342496144551901</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5">
-        <v>1.5842594036493889E-2</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1.451952742491645E-2</v>
-      </c>
-      <c r="D7" s="6">
-        <v>4.0791559341348711E-3</v>
-      </c>
-      <c r="E7" s="5">
-        <v>2.861970781639005E-2</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1.8989605295222541E-2</v>
+      <c r="B7" s="3">
+        <v>1.5842594036493251E-2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.451952742491654E-2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.0791559341349396E-3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.8619707816389481E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.89896052952226E-2</v>
       </c>
       <c r="G7" s="7">
-        <v>0.31003393709722399</v>
+        <v>0.3100339370972347</v>
       </c>
       <c r="H7" s="7">
-        <v>0.61488761527220026</v>
+        <v>0.61488761527185987</v>
       </c>
       <c r="I7" s="7">
-        <v>0.1047182822391298</v>
+        <v>0.10471828223913091</v>
       </c>
       <c r="J7" s="9">
-        <v>0.47301294431852642</v>
+        <v>0.47301294431852808</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5">
-        <v>1.269488451179907E-2</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1.2804264738281871E-2</v>
-      </c>
-      <c r="D8" s="6">
-        <v>3.396663088587147E-3</v>
-      </c>
-      <c r="E8" s="5">
-        <v>2.6744688287310841E-2</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1.5955340961895201E-2</v>
+      <c r="B8" s="3">
+        <v>1.269488451179846E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.2804264738281741E-2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3.3966630885856222E-3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.6744688287310189E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.5955340961887131E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>0.28379897357115191</v>
+        <v>0.28379897357114908</v>
       </c>
       <c r="H8" s="7">
-        <v>0.55632871049662691</v>
+        <v>0.55632871049642285</v>
       </c>
       <c r="I8" s="7">
-        <v>9.4230868935787387E-2</v>
+        <v>9.4230868935780129E-2</v>
       </c>
       <c r="J8" s="9">
-        <v>0.40815321635445773</v>
+        <v>0.40815321635444979</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5">
-        <v>1.156827856213515E-2</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1.483675974119658E-2</v>
-      </c>
-      <c r="D9" s="6">
-        <v>3.572976462353441E-3</v>
-      </c>
-      <c r="E9" s="5">
-        <v>2.823243751013086E-2</v>
-      </c>
-      <c r="F9" s="5">
-        <v>3.2771705124711427E-2</v>
+      <c r="B9" s="3">
+        <v>1.156827856213514E-2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.48367597411969E-2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3.5729764623534249E-3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.823243751013153E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.2771705124712593E-2</v>
       </c>
       <c r="G9" s="7">
-        <v>0.27633354840683683</v>
+        <v>0.27633354840684582</v>
       </c>
       <c r="H9" s="7">
-        <v>0.66806836242089096</v>
+        <v>0.6680683624209065</v>
       </c>
       <c r="I9" s="7">
-        <v>7.3122191365065134E-2</v>
+        <v>7.3122191365069381E-2</v>
       </c>
       <c r="J9" s="9">
-        <v>0.36224140525310122</v>
+        <v>0.36224140525309662</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
-        <v>2.8430993791853832E-3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>3.102118842287139E-3</v>
-      </c>
-      <c r="D10" s="6">
-        <v>4.1896370686821929E-4</v>
-      </c>
-      <c r="E10" s="5">
-        <v>5.8675379464999183E-3</v>
-      </c>
-      <c r="F10" s="5">
-        <v>2.2867146080668621E-3</v>
+      <c r="B10" s="3">
+        <v>2.8463112150507921E-3</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.038049334208153E-3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4.2257893090471177E-4</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.870733968789908E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.2695144632461591E-3</v>
       </c>
       <c r="G10" s="7">
-        <v>5.443027283787847E-2</v>
+        <v>5.2751668212520773E-2</v>
       </c>
       <c r="H10" s="7">
-        <v>3.5840953042514667E-2</v>
+        <v>3.5257390623251839E-2</v>
       </c>
       <c r="I10" s="7">
-        <v>4.5588004840147127E-2</v>
+        <v>4.5438789038981457E-2</v>
       </c>
       <c r="J10" s="9">
-        <v>0.17733154542528781</v>
+        <v>0.17441867582393969</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5">
-        <v>2.265752430158096E-3</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2.699456497917265E-3</v>
-      </c>
-      <c r="D11" s="6">
-        <v>3.2802714390220682E-4</v>
-      </c>
-      <c r="E11" s="5">
-        <v>4.8117159809229039E-3</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2.063799036112232E-3</v>
+      <c r="B11" s="3">
+        <v>2.256452358528871E-3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.6241821757344778E-3</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3.2951914190818801E-4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.7963734326576706E-3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.037185420198942E-3</v>
       </c>
       <c r="G11" s="7">
-        <v>4.5539591528430727E-2</v>
+        <v>4.3835092476100831E-2</v>
       </c>
       <c r="H11" s="7">
-        <v>3.4751045785803437E-2</v>
+        <v>3.3845249376898652E-2</v>
       </c>
       <c r="I11" s="7">
-        <v>2.984803439380148E-2</v>
+        <v>2.9821856063730862E-2</v>
       </c>
       <c r="J11" s="9">
-        <v>0.1089697717730355</v>
+        <v>0.10696597067088209</v>
       </c>
     </row>
   </sheetData>
